--- a/frontend/public/DATA_YANG_PERLU_DIISI_DA_FOKUS.xlsx
+++ b/frontend/public/DATA_YANG_PERLU_DIISI_DA_FOKUS.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -580,57 +580,64 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Varian yang belum punya BOM: aksesorisnya sudah disalin (biru) dari BOM varian lain model yang sama — periksa, ubah bila berbeda.</t>
+          <t xml:space="preserve">     Varian yang belum punya BOM, atau BOM-nya belum punya aksesoris: aksesorisnya sudah disalin (biru) dari BOM varian lain model yang sama — periksa, ubah bila berbeda.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Sheet BOM_OTOMATIS — kelompok yang sudah diisi otomatis oleh sistem (varian biru) atau selesai lewat sheet lain (VARIAN_BARU/MATERIAL).</t>
+          <t xml:space="preserve">     Kelengkapan dinilai PER VARIAN: model dianggap lengkap hanya bila SEMUA variannya punya BOM ber-aksesoris (kolom varian_tanpa_aksesoris di RINGKASAN).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Tidak ada sel kuning di sana: cukup periksa. Sheet ini IKUT DITERAPKAN saat diunggah balik — biarkan apa adanya, jangan dihapus.</t>
+          <t xml:space="preserve">     Sheet BOM_OTOMATIS — kelompok yang sudah diisi otomatis oleh sistem (varian biru) atau selesai lewat sheet lain (VARIAN_BARU/MATERIAL).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Sheet MATERIAL — bahan yang harganya masih 0 atau isi kemasannya belum diketahui. Isi 'harga_per_satuan_beli' (harga 1 roll / 1 m / 1 pack)</t>
+          <t xml:space="preserve">     Tidak ada sel kuning di sana: cukup periksa. Sheet ini IKUT DITERAPKAN saat diunggah balik — biarkan apa adanya, jangan dihapus.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">  3. Sheet MATERIAL — bahan yang harganya masih 0 atau isi kemasannya belum diketahui. Isi 'harga_per_satuan_beli' (harga 1 roll / 1 m / 1 pack)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">     dan, bila diminta, 'isi_per_satuan_beli' = berapa pcs dalam 1 roll/pack. satuan_beli sudah diisi sama dengan satuan dasar.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>UNGGAH BALIK berkas ini di Portal Keuangan → Master Akuntansi → Impor Harga · Rekening · BOM → 'Terapkan semua sheet'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Baris yang sel kuningnya dibiarkan kosong TIDAK diubah — aman diunggah sebagian, lalu unduh lagi berkas FOKUS untuk sisanya.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Baris yang sel kuningnya dibiarkan kosong TIDAK diubah — aman diunggah sebagian, lalu unduh lagi berkas FOKUS untuk sisanya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Kode bahan lihat sheet REF_AKSESORIS (hanya referensi, tidak perlu diisi).</t>
         </is>
@@ -647,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -655,10 +662,11 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,20 +697,25 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>varian_tanpa_aksesoris</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>aksesoris_di_bom</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>isi_di_sheet</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>di_berkas_anda</t>
         </is>
@@ -711,12 +724,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DA-1209</t>
+          <t>DA-1101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lunara</t>
+          <t>Lyora</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -725,27 +738,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>sebagian</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+          <t>1 dari 6 varian BOM-nya belum punya aksesoris</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS (baris biru disalin dari varian lain — periksa)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -754,7 +770,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DA-1210</t>
+          <t>DA-1209</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,22 +789,25 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -797,7 +816,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DA-1211</t>
+          <t>DA-1210</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,22 +835,25 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -840,12 +862,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DA-1401</t>
+          <t>DA-1211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rachel set</t>
+          <t>Lunara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -854,27 +876,30 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS</t>
+          <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -883,12 +908,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DA-1509</t>
+          <t>DA-1401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hanny</t>
+          <t>Rachel set</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -897,27 +922,30 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2 dari 13 varian belum punya BOM</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS (baris biru disalin dari varian lain — periksa)</t>
+          <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -926,12 +954,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DA-1510</t>
+          <t>DA-1509</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hanni</t>
+          <t>Hanny</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -945,22 +973,25 @@
       <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>2 dari 13 varian belum punya BOM</t>
-        </is>
-      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS (baris biru disalin dari varian lain — periksa)</t>
+          <t>BOM ada, aksesoris belum diisi (2 dari 13 varian juga belum punya BOM)</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -969,41 +1000,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DA-2102</t>
+          <t>DA-1510</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Hanni</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>One set</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t>BOM ada, aksesoris belum diisi (2 dari 13 varian juga belum punya BOM)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1012,7 +1046,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DA-2103</t>
+          <t>DA-2102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1031,65 +1065,71 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>DA-2104</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>GIA</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DA-2103</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Dress</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>— (aktifkan SKU dulu bila masih dijual)</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>BOM ada, aksesoris belum diisi</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1098,12 +1138,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>DA-2107</t>
+          <t>DA-2104</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Luvia</t>
+          <t>GIA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1117,22 +1157,25 @@
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>— (aktifkan SKU dulu bila masih dijual)</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1141,84 +1184,90 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>DA-2107</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Luvia</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>— (aktifkan SKU dulu bila masih dijual)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>DA-2108</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Maudy</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Dress</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>— (aktifkan SKU dulu bila masih dijual)</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DA-2112</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Heidi</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dress</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1227,12 +1276,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DA-2113</t>
+          <t>DA-2112</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Riana</t>
+          <t>Heidi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1246,22 +1295,25 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1270,12 +1322,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DA-2201</t>
+          <t>DA-2113</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ona</t>
+          <t>Riana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1284,27 +1336,30 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>belum punya BOM sama sekali (7 varian)</t>
-        </is>
-      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS (aksesoris) + R&amp;D → BOM (kain)</t>
+          <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1313,12 +1368,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DA-2202</t>
+          <t>DA-2201</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Ona</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1330,24 +1385,27 @@
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS</t>
+          <t>belum punya BOM sama sekali (7 varian)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS (aksesoris) + R&amp;D → BOM (kain)</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1356,127 +1414,136 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>DA-2202</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Freya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dress</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>BOM ada, aksesoris belum diisi</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>DA-2401</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Brigitta</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Dress</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>DA-2501</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Erlyna</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Dress</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>— (aktifkan SKU dulu bila masih dijual)</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DA-2506</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Azkia</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dress</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1485,7 +1552,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DA-2507</t>
+          <t>DA-2506</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1504,22 +1571,25 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1528,17 +1598,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DA-3301</t>
+          <t>DA-2507</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aruna</t>
+          <t>Azkia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blouse</t>
+          <t>Dress</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1547,22 +1617,25 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1571,7 +1644,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DA-3302</t>
+          <t>DA-3301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1590,22 +1663,25 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1614,12 +1690,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DA-3401</t>
+          <t>DA-3302</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vonny</t>
+          <t>Aruna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1628,27 +1704,30 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS</t>
+          <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1657,12 +1736,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DA-3504</t>
+          <t>DA-3401</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thea</t>
+          <t>Vonny</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1671,27 +1750,30 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1700,7 +1782,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DA-3505</t>
+          <t>DA-3504</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1719,22 +1801,25 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1743,7 +1828,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DA-3506</t>
+          <t>DA-3505</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1762,22 +1847,25 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1786,7 +1874,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DA-3507</t>
+          <t>DA-3506</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1805,22 +1893,25 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1829,84 +1920,90 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>DA-3507</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Blouse</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>BOM ada, aksesoris belum diisi</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>DA-3512</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0,5 Jenifer</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Blouse</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>DA-3601</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Airyn</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Blouse</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>— (aktifkan SKU dulu bila masih dijual)</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1915,84 +2012,90 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>DA-3601</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Airyn</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Blouse</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>— (aktifkan SKU dulu bila masih dijual)</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>DA-3602</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Jeslyn</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Blouse</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>semua SKU nonaktif (sudah tidak dijual) — tidak perlu BOM</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>— (aktifkan SKU dulu bila masih dijual)</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DA-3603</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Mecca</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Blouse</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>BOM_AKSESORIS</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2001,12 +2104,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DA-3604</t>
+          <t>DA-3603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Mecca</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2015,27 +2118,30 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2044,7 +2150,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DA-3605</t>
+          <t>DA-3604</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2063,22 +2169,25 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2087,12 +2196,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DA-3701</t>
+          <t>DA-3605</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rasha</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2101,27 +2210,30 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
-        </is>
-      </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+          <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2130,7 +2242,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DA-3702</t>
+          <t>DA-3701</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2149,22 +2261,25 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2173,41 +2288,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DA-4101</t>
+          <t>DA-3702</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Liana</t>
+          <t>Rasha</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Blouse</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS</t>
+          <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2216,7 +2334,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DA-4102</t>
+          <t>DA-4101</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2235,22 +2353,25 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2259,12 +2380,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DA-4106</t>
+          <t>DA-4102</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Liana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2273,27 +2394,30 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
-        </is>
-      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+          <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2302,7 +2426,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DA-4107</t>
+          <t>DA-4106</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2321,22 +2445,25 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2345,12 +2472,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DA-4201</t>
+          <t>DA-4107</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nagita top</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2359,27 +2486,30 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>BOM ada, aksesoris belum diisi</t>
-        </is>
-      </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>BOM_AKSESORIS</t>
+          <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2388,7 +2518,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DA-4202</t>
+          <t>DA-4201</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2407,22 +2537,25 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2431,12 +2564,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DA-4203</t>
+          <t>DA-4202</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ziva</t>
+          <t>Nagita top</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2450,22 +2583,25 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2474,12 +2610,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DA-4305</t>
+          <t>DA-4203</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arka</t>
+          <t>Ziva</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2488,27 +2624,30 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>belum punya varian/SKU sama sekali</t>
-        </is>
-      </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+          <t>BOM ada, aksesoris belum diisi</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2517,12 +2656,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DA-4306</t>
+          <t>DA-4305</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Irana</t>
+          <t>Arka</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2536,22 +2675,25 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2560,7 +2702,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DA-4307</t>
+          <t>DA-4306</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2579,22 +2721,25 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2603,17 +2748,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DA-6401</t>
+          <t>DA-4307</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aro</t>
+          <t>Irana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inner</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2622,22 +2767,25 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2646,12 +2794,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DA-6901</t>
+          <t>DA-6401</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Inner jersey</t>
+          <t>Aro</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2665,22 +2813,25 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2689,41 +2840,90 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>DA-6901</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Inner jersey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Inner</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>belum punya varian/SKU sama sekali</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>DA-7101</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Jolie Tunik</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Tunik</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>tidak</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>belum punya varian/SKU sama sekali</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>VARIAN_BARU (warna+ukuran) lalu BOM_AKSESORIS</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3412,7 +3612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3482,78 +3682,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DA-1209</t>
+          <t>DA-1101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lunara</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Lyora</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>A-KRT-0003</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Karet Uk 3 cm 1 Meter</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>BURGUNDY ALLSIZE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Warna: BURGUNDY, CARAMEL, GREY, HITAM, MAGENTA, MAHOGANY · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+          <t>varian DA-1101-BRG-ALLSIZE BOM-nya belum punya aksesoris — aksesoris disalin dari BOM varian lain; periksa, ubah bila berbeda, lalu unggah (aksesoris ditambahkan ke BOM varian ini)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>A-R45-0001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rit Besi uk 45cm warna Hitam</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>A-BIS-0001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bisban warna hitam 1 Roll 21,919</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DA-1210</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>A-LBL-0004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Label DA 1 Roll</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DA-1209</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Lunara</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="6" t="n"/>
@@ -3561,7 +3821,11 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -3576,16 +3840,8 @@
       <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DA-1211</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lunara</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="6" t="n"/>
@@ -3593,15 +3849,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DA-1210</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lunara</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="6" t="n"/>
@@ -3609,7 +3869,11 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -3624,36 +3888,28 @@
       <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DA-1401</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rachel set</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Warna: BUTTER YELLOW, DUSTY, MAHOGANY, MAROON · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DA-1211</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lunara</t>
+        </is>
+      </c>
       <c r="C12" s="6" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="6" t="n"/>
@@ -3661,7 +3917,11 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -3676,48 +3936,44 @@
       <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DA-1509</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Hanny</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Digital Paint abstrak M</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>varian DA-1509-DGP-M belum punya BOM — isi kode_material &amp; qty_per_pcs aksesorisnya</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DA-1401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rachel set</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Warna: BUTTER YELLOW, DUSTY, MAHOGANY, MAROON · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -3732,48 +3988,44 @@
       <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DA-1509</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hanny</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Pita merah M</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>varian DA-1509-PMR-M belum punya BOM — isi kode_material &amp; qty_per_pcs aksesorisnya</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DA-1509</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hanny</t>
+        </is>
+      </c>
       <c r="C18" s="6" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu; 2 varian yang belum punya BOM dibuat otomatis saat diunggah</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -3788,48 +4040,44 @@
       <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DA-1510</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Hanni</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Digital Paint abstrak XL</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>varian DA-1510-DGP-XL belum punya BOM — isi kode_material &amp; qty_per_pcs aksesorisnya</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DA-1510</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hanni</t>
+        </is>
+      </c>
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu; 2 varian yang belum punya BOM dibuat otomatis saat diunggah</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -3844,48 +4092,44 @@
       <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DA-1510</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hanni</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Pita merah XL</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Warna: Baby fushia, Black Purple, Bunga Pelangi, Digital Bunga Emas, Digital Paint abstrak, Digital Ratih, Leopard hitam, Pita merah, Polkadot putih, Rainbow, Red Elegant, Scarlet, polkadot hitam · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>varian DA-1510-PMR-XL belum punya BOM — isi kode_material &amp; qty_per_pcs aksesorisnya</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DA-2102</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Warna: BATA, BURGUNDY, CREAM, GREY, HIJAU BOTOL, HITAM, KHAKI, MAGENTA, MOCA, OLIVE · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -3900,44 +4144,44 @@
       <c r="J25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DA-2102</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Warna: BATA, BURGUNDY, CREAM, GREY, HIJAU BOTOL, HITAM, KHAKI, MAGENTA, MOCA, OLIVE · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DA-2103</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Warna: BATA, BURGUNDY, CREAM, GREY, HIJAU BOTOL, HITAM, KHAKI, MAGENTA, MOCA, OLIVE · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -3952,36 +4196,28 @@
       <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DA-2103</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="6" t="n"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Warna: BATA, BURGUNDY, CREAM, GREY, HIJAU BOTOL, HITAM, KHAKI, MAGENTA, MOCA, OLIVE · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DA-2112</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Heidi</t>
+        </is>
+      </c>
       <c r="C30" s="6" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="6" t="n"/>
@@ -3989,7 +4225,11 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -4004,16 +4244,8 @@
       <c r="J31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DA-2112</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Heidi</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="6" t="n"/>
@@ -4021,15 +4253,19 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DA-2113</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Riana</t>
+        </is>
+      </c>
       <c r="C33" s="6" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="6" t="n"/>
@@ -4037,7 +4273,11 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -4052,16 +4292,8 @@
       <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DA-2113</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Riana</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="6" t="n"/>
@@ -4069,23 +4301,35 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DA-2201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ona</t>
+        </is>
+      </c>
       <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya BOM sama sekali (7 varian) — isi kode_material &amp; qty_per_pcs aksesoris (varian kosong = semua varian); kain/potongan dilengkapi di R&amp;D → BOM</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -4100,44 +4344,44 @@
       <c r="J37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>DA-2201</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ona</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="6" t="n"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya BOM sama sekali (7 varian) — isi kode_material &amp; qty_per_pcs aksesoris (varian kosong = semua varian); kain/potongan dilengkapi di R&amp;D → BOM</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DA-2202</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Freya</t>
+        </is>
+      </c>
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="6" t="n"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -4152,44 +4396,44 @@
       <c r="J40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>DA-2202</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Freya</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="6" t="n"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DA-2401</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brigitta</t>
+        </is>
+      </c>
       <c r="C42" s="6" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="6" t="n"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -4204,36 +4448,28 @@
       <c r="J43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DA-2401</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brigitta</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="6" t="n"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DA-2506</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Azkia</t>
+        </is>
+      </c>
       <c r="C45" s="6" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="6" t="n"/>
@@ -4241,7 +4477,11 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -4256,16 +4496,8 @@
       <c r="J46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DA-2506</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Azkia</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="6" t="n"/>
@@ -4273,15 +4505,19 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DA-2507</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Azkia</t>
+        </is>
+      </c>
       <c r="C48" s="6" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="6" t="n"/>
@@ -4289,7 +4525,11 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -4304,16 +4544,8 @@
       <c r="J49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>DA-2507</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Azkia</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="6" t="n"/>
@@ -4321,15 +4553,19 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DA-3301</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Aruna</t>
+        </is>
+      </c>
       <c r="C51" s="6" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="6" t="n"/>
@@ -4337,7 +4573,11 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -4352,16 +4592,8 @@
       <c r="J52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>DA-3301</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Aruna</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="6" t="n"/>
@@ -4369,15 +4601,19 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DA-3302</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Aruna</t>
+        </is>
+      </c>
       <c r="C54" s="6" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n"/>
@@ -4385,7 +4621,11 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -4400,16 +4640,8 @@
       <c r="J55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>DA-3302</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Aruna</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="6" t="n"/>
@@ -4417,23 +4649,35 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DA-3401</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Vonny</t>
+        </is>
+      </c>
       <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="6" t="n"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Warna: BUTTER YELLOW, DENIM, DUSTY, MAROON · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -4448,44 +4692,44 @@
       <c r="J58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DA-3401</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Vonny</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="6" t="n"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Warna: BUTTER YELLOW, DENIM, DUSTY, MAROON · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DA-3504</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
       <c r="C60" s="6" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" s="6" t="n"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -4500,44 +4744,44 @@
       <c r="J61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>DA-3504</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="6" t="n"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DA-3505</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
       <c r="C63" s="6" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="6" t="n"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: L</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4552,44 +4796,44 @@
       <c r="J64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>DA-3505</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="6" t="n"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: L</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DA-3506</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
       <c r="C66" s="6" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="6" t="n"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4604,44 +4848,44 @@
       <c r="J67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>DA-3506</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" s="6" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="6" t="n"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DA-3507</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Thea</t>
+        </is>
+      </c>
       <c r="C69" s="6" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="6" t="n"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: XXL</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4656,36 +4900,28 @@
       <c r="J70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>DA-3507</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Thea</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" s="6" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="6" t="n"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Warna: Polkadot putih, polkadot hitam · Ukuran: XXL</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DA-3512</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0,5 Jenifer</t>
+        </is>
+      </c>
       <c r="C72" s="6" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="6" t="n"/>
@@ -4693,7 +4929,11 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4708,16 +4948,8 @@
       <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>DA-3512</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>0,5 Jenifer</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" s="6" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="6" t="n"/>
@@ -4725,23 +4957,35 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DA-3603</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Mecca</t>
+        </is>
+      </c>
       <c r="C75" s="6" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="6" t="n"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Warna: HITAM, KHAKI, OLIVE · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4756,44 +5000,44 @@
       <c r="J76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>DA-3603</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Mecca</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" s="6" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="6" t="n"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Warna: HITAM, KHAKI, OLIVE · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DA-3604</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
       <c r="C78" s="6" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="6" t="n"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, HITAM, MAUVE, PUTIH · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4808,44 +5052,44 @@
       <c r="J79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>DA-3604</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" s="6" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="6" t="n"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, HITAM, MAUVE, PUTIH · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DA-3605</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
       <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="6" t="n"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" s="3" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, HITAM, MAUVE, PUTIH · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -4860,36 +5104,28 @@
       <c r="J82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>DA-3605</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="6" t="n"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, HITAM, MAUVE, PUTIH · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DA-3701</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rasha</t>
+        </is>
+      </c>
       <c r="C84" s="6" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="6" t="n"/>
@@ -4897,7 +5133,11 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -4912,16 +5152,8 @@
       <c r="J85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>DA-3701</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Rasha</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" s="6" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="6" t="n"/>
@@ -4929,15 +5161,19 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DA-3702</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Rasha</t>
+        </is>
+      </c>
       <c r="C87" s="6" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" s="6" t="n"/>
@@ -4945,7 +5181,11 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -4960,16 +5200,8 @@
       <c r="J88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>DA-3702</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Rasha</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" s="6" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="6" t="n"/>
@@ -4977,23 +5209,35 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DA-4101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Liana</t>
+        </is>
+      </c>
       <c r="C90" s="6" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="6" t="n"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" s="3" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Warna: BURGUNDY, CARAMEL, GREY, HITAM, MAHOGANY · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -5008,44 +5252,44 @@
       <c r="J91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>DA-4101</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Liana</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" s="6" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" s="6" t="n"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Warna: BURGUNDY, CARAMEL, GREY, HITAM, MAHOGANY · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DA-4102</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Liana</t>
+        </is>
+      </c>
       <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="6" t="n"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Warna: BURGUNDY, CARAMEL, GREY, HITAM, MAHOGANY · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -5060,36 +5304,28 @@
       <c r="J94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DA-4102</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Liana</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" s="6" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" s="6" t="n"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Warna: BURGUNDY, CARAMEL, GREY, HITAM, MAHOGANY · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DA-4106</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cleo</t>
+        </is>
+      </c>
       <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" s="6" t="n"/>
@@ -5097,7 +5333,11 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -5112,16 +5352,8 @@
       <c r="J97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>DA-4106</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cleo</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" s="6" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" s="6" t="n"/>
@@ -5129,15 +5361,19 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DA-4107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cleo</t>
+        </is>
+      </c>
       <c r="C99" s="6" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" s="6" t="n"/>
@@ -5145,7 +5381,11 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -5160,16 +5400,8 @@
       <c r="J100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>DA-4107</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cleo</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" s="6" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" s="6" t="n"/>
@@ -5177,23 +5409,35 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DA-4201</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Nagita top</t>
+        </is>
+      </c>
       <c r="C102" s="6" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" s="6" t="n"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" s="3" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: M</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -5208,44 +5452,44 @@
       <c r="J103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>DA-4201</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Nagita top</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" s="6" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" s="6" t="n"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: M</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DA-4202</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Nagita top</t>
+        </is>
+      </c>
       <c r="C105" s="6" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" s="6" t="n"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" s="3" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: XL</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -5260,44 +5504,44 @@
       <c r="J106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>DA-4202</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Nagita top</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" s="6" t="n"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: XL</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DA-4203</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ziva</t>
+        </is>
+      </c>
       <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" s="6" t="n"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" s="3" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; varian kosong = semua varian; tambah baris bila perlu</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -5312,36 +5556,28 @@
       <c r="J109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>DA-4203</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Ziva</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" s="6" t="n"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Warna: CREAM, DENIM, DUSTY, GREY, HITAM, MAGENTA, MOCA · Ukuran: ALLSIZE</t>
-        </is>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>belum ada aksesoris di BOM — isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs; tambah baris bila perlu</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DA-4305</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Arka</t>
+        </is>
+      </c>
       <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" s="6" t="n"/>
@@ -5349,7 +5585,11 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -5364,16 +5604,8 @@
       <c r="J112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>DA-4305</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Arka</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" s="6" t="n"/>
@@ -5381,15 +5613,19 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DA-4306</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Irana</t>
+        </is>
+      </c>
       <c r="C114" s="6" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="6" t="n"/>
@@ -5397,7 +5633,11 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -5412,16 +5652,8 @@
       <c r="J115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>DA-4306</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Irana</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" s="6" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" s="6" t="n"/>
@@ -5429,15 +5661,19 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DA-4307</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Irana</t>
+        </is>
+      </c>
       <c r="C117" s="6" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" s="6" t="n"/>
@@ -5445,7 +5681,11 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -5460,16 +5700,8 @@
       <c r="J118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>DA-4307</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Irana</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" s="6" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" s="6" t="n"/>
@@ -5477,15 +5709,19 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DA-6401</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Aro</t>
+        </is>
+      </c>
       <c r="C120" s="6" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" s="6" t="n"/>
@@ -5493,7 +5729,11 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -5508,16 +5748,8 @@
       <c r="J121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>DA-6401</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Aro</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" s="6" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" s="6" t="n"/>
@@ -5525,15 +5757,19 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DA-6901</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Inner jersey</t>
+        </is>
+      </c>
       <c r="C123" s="6" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" s="6" t="n"/>
@@ -5541,7 +5777,11 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -5556,16 +5796,8 @@
       <c r="J124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>DA-6901</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Inner jersey</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" s="6" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="6" t="n"/>
@@ -5573,15 +5805,19 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
+      <c r="J125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DA-7101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Jolie Tunik</t>
+        </is>
+      </c>
       <c r="C126" s="6" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" s="6" t="n"/>
@@ -5589,7 +5825,11 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -5604,16 +5844,8 @@
       <c r="J127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>DA-7101</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Jolie Tunik</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" s="6" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" s="6" t="n"/>
@@ -5621,35 +5853,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>model belum punya SKU — isi dulu sheet VARIAN_BARU (kode_warna + ukuran), lalu isi kode_material (lihat REF_AKSESORIS) &amp; qty_per_pcs di sini; varian kosong = semua varian. Kedua sheet diterapkan dalam satu unggahan</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" s="6" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" s="3" t="inlineStr"/>
+      <c r="J128" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
